--- a/Documents/Short Product Plan.xlsx
+++ b/Documents/Short Product Plan.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\umama\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06C5A85-40D0-4971-9609-0F37F3280469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7DF1B4E-3EDE-40BD-931B-6778D7743EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Product Overview" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="103">
   <si>
     <t>Item</t>
   </si>
@@ -133,18 +133,9 @@
     <t>v1.1</t>
   </si>
   <si>
-    <t>Authentication, Dashboard MVP</t>
-  </si>
-  <si>
-    <t>Analytics export, Notification system</t>
-  </si>
-  <si>
     <t>None</t>
   </si>
   <si>
-    <t>Requires API upgrade</t>
-  </si>
-  <si>
     <t>On Track</t>
   </si>
   <si>
@@ -182,9 +173,6 @@
   </si>
   <si>
     <t>US3</t>
-  </si>
-  <si>
-    <t>Yet to Plan</t>
   </si>
   <si>
     <t>Net time what will you do differently</t>
@@ -337,6 +325,48 @@
 → Build, maintain, and improve the system
 4.External Systems / Integrations (Tally, OCR/AI tools, GST APIs)
 → Support data extraction, validation, and accounting integration</t>
+  </si>
+  <si>
+    <t>Frontend Setup (UI), Authentication/Login System</t>
+  </si>
+  <si>
+    <t>Review &amp; Approve Module (CA validation, Edit extracted data)</t>
+  </si>
+  <si>
+    <t>Tally Export (Excel/CSV structured output)</t>
+  </si>
+  <si>
+    <t>Data Isolation (Client-wise data separation, security)</t>
+  </si>
+  <si>
+    <t>Database Setup</t>
+  </si>
+  <si>
+    <t>File Storage (Cloud/Local)</t>
+  </si>
+  <si>
+    <t>OCR API / AI Model</t>
+  </si>
+  <si>
+    <t>UI + Backend Validation Logic</t>
+  </si>
+  <si>
+    <t>Export Module, Tally Format Rules</t>
+  </si>
+  <si>
+    <t>Database Design, Access Control</t>
+  </si>
+  <si>
+    <t>planned</t>
+  </si>
+  <si>
+    <t>Client Management (Add clients, list clients, Delete Clients)</t>
+  </si>
+  <si>
+    <t>Invoice Upload (PDF,JPG,PNG,multiple files)</t>
+  </si>
+  <si>
+    <t>AI Extraction (Call AI model model,extract structured data)</t>
   </si>
 </sst>
 </file>
@@ -401,7 +431,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -416,6 +446,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -741,23 +774,23 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
@@ -765,7 +798,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -801,10 +834,10 @@
         <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -819,39 +852,39 @@
         <v>10</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -868,7 +901,7 @@
         <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>19</v>
@@ -880,13 +913,13 @@
         <v>21</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -895,7 +928,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -910,7 +943,7 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -925,7 +958,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -940,7 +973,7 @@
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -955,7 +988,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -983,7 +1016,7 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -1027,12 +1060,12 @@
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -1044,7 +1077,7 @@
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -1109,10 +1142,10 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -1122,7 +1155,7 @@
         <v>19</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E21" s="5"/>
     </row>
@@ -1131,25 +1164,25 @@
         <v>20</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E23" s="5"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E24" s="5"/>
     </row>
@@ -1160,23 +1193,23 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D27" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D28" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1191,8 +1224,8 @@
   <cols>
     <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
-    <col min="4" max="4" width="21.21875" customWidth="1"/>
+    <col min="3" max="3" width="52" customWidth="1"/>
+    <col min="4" max="4" width="30.6640625" customWidth="1"/>
     <col min="5" max="5" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1201,7 +1234,7 @@
         <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>32</v>
@@ -1210,89 +1243,101 @@
         <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B3" s="3">
-        <v>45976</v>
+        <v>46128</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B4" s="3">
-        <v>45983</v>
+        <v>46129</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B5" s="3">
-        <v>45990</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+        <v>46130</v>
+      </c>
+      <c r="C5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
       <c r="E5" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B6" s="3">
-        <v>45997</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+        <v>46131</v>
+      </c>
+      <c r="C6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>95</v>
+      </c>
       <c r="E6" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B7" s="3">
-        <v>46004</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+        <v>46132</v>
+      </c>
+      <c r="C7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>96</v>
+      </c>
       <c r="E7" s="2" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1300,12 +1345,16 @@
         <v>34</v>
       </c>
       <c r="B8" s="3">
-        <v>46011</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+        <v>46133</v>
+      </c>
+      <c r="C8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" t="s">
+        <v>97</v>
+      </c>
       <c r="E8" s="2" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1313,12 +1362,16 @@
         <v>35</v>
       </c>
       <c r="B9" s="3">
-        <v>46018</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+        <v>46134</v>
+      </c>
+      <c r="C9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" t="s">
+        <v>98</v>
+      </c>
       <c r="E9" s="2" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1346,12 +1399,12 @@
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1372,7 +1425,7 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D6" s="1"/>
     </row>
@@ -1387,7 +1440,7 @@
         <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">

--- a/Documents/Short Product Plan.xlsx
+++ b/Documents/Short Product Plan.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\umama\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7DF1B4E-3EDE-40BD-931B-6778D7743EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B788567-BF7A-47C7-AE45-8A14730FBA54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Product Overview" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="125">
   <si>
     <t>Item</t>
   </si>
@@ -109,15 +109,6 @@
     <t>Improvements / Action Items</t>
   </si>
   <si>
-    <t>Team collaboration was great</t>
-  </si>
-  <si>
-    <t>Test coverage was low</t>
-  </si>
-  <si>
-    <t>Automate test pipeline in next sprint</t>
-  </si>
-  <si>
     <t>Release</t>
   </si>
   <si>
@@ -236,32 +227,6 @@
   </si>
   <si>
     <t>Llist Epic Names</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Note:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> This is for the team to learn and improve. I have taught you in the class on Nov 4, 2025.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">           Ideally, the team should do this at the end of every release. How often you do , I leave it to you.</t>
   </si>
   <si>
     <t>Product Vision/ Purpose</t>
@@ -367,6 +332,87 @@
   </si>
   <si>
     <t>AI Extraction (Call AI model model,extract structured data)</t>
+  </si>
+  <si>
+    <t>Strong understanding of MSME customer pain points through interviews</t>
+  </si>
+  <si>
+    <t>Test coverage and validation scenarios were limited</t>
+  </si>
+  <si>
+    <t>Increase test coverage for all invoice types (PDF, image, handwritten, WhatsApp)</t>
+  </si>
+  <si>
+    <t>Clear problem definition (manual entry, GST errors, messy data)</t>
+  </si>
+  <si>
+    <t>Limited real-time validation during demo scenarios</t>
+  </si>
+  <si>
+    <t>Add real-time validation checks for GSTIN, missing fields, duplicates</t>
+  </si>
+  <si>
+    <t>Dev Team</t>
+  </si>
+  <si>
+    <t>Well-defined target users (CAs and MSMEs)</t>
+  </si>
+  <si>
+    <t>Some edge cases (incomplete invoices, unclear handwriting) not fully handled</t>
+  </si>
+  <si>
+    <t>Improve AI model to handle incomplete and low-quality data better</t>
+  </si>
+  <si>
+    <t>AI/ML Team</t>
+  </si>
+  <si>
+    <t>Good feature design (bulk upload, WhatsApp, email integration)</t>
+  </si>
+  <si>
+    <t>Integration with tools like Tally not fully tested end-to-end</t>
+  </si>
+  <si>
+    <t>Perform full integration testing with Tally export and real datasets</t>
+  </si>
+  <si>
+    <t>Backend Team</t>
+  </si>
+  <si>
+    <t>Identified key GST challenges (rates, compliance, ITC confusion)</t>
+  </si>
+  <si>
+    <t>Performance not tested for large-scale invoice volume</t>
+  </si>
+  <si>
+    <t>Conduct load testing for bulk uploads and high-volume processing</t>
+  </si>
+  <si>
+    <t>QA Team</t>
+  </si>
+  <si>
+    <t>Clear identification of customer workflow (collection → entry → filing)</t>
+  </si>
+  <si>
+    <t>Time-saving benefits not fully measured in testing</t>
+  </si>
+  <si>
+    <t>Add metrics dashboard to track time saved and efficiency improvements</t>
+  </si>
+  <si>
+    <t>Analytics Team</t>
+  </si>
+  <si>
+    <t>Multi-source input support (PDF, image, WhatsApp, email)</t>
+  </si>
+  <si>
+    <t>Lack of automation in GST filing workflow</t>
+  </si>
+  <si>
+    <t>Add automation features for GST-ready invoice export and filing support</t>
+  </si>
+  <si>
+    <t>Product Team</t>
   </si>
 </sst>
 </file>
@@ -774,23 +820,23 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
@@ -798,7 +844,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -834,10 +880,10 @@
         <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -852,39 +898,39 @@
         <v>10</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -901,7 +947,7 @@
         <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>19</v>
@@ -913,13 +959,13 @@
         <v>21</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -928,7 +974,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -943,7 +989,7 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -958,7 +1004,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -973,7 +1019,7 @@
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -988,7 +1034,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -1016,7 +1062,7 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -1060,12 +1106,12 @@
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -1077,7 +1123,7 @@
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -1142,10 +1188,10 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -1155,7 +1201,7 @@
         <v>19</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E21" s="5"/>
     </row>
@@ -1164,25 +1210,25 @@
         <v>20</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E23" s="5"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E24" s="5"/>
     </row>
@@ -1193,23 +1239,23 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D27" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D28" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1231,147 +1277,147 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B3" s="3">
         <v>46128</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B4" s="3">
         <v>46129</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B5" s="3">
         <v>46130</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B6" s="3">
         <v>46131</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B7" s="3">
         <v>46132</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B8" s="3">
         <v>46133</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B9" s="3">
         <v>46134</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1388,23 +1434,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A2:D13"/>
+  <dimension ref="A3:D13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" customWidth="1"/>
-    <col min="3" max="3" width="31.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.44140625" customWidth="1"/>
+    <col min="1" max="1" width="60.21875" customWidth="1"/>
+    <col min="2" max="2" width="64" customWidth="1"/>
+    <col min="3" max="3" width="71.33203125" customWidth="1"/>
+    <col min="4" max="4" width="25.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>71</v>
-      </c>
-    </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1425,59 +1466,107 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="A8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+      <c r="A9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="A10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+      <c r="A11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" t="s">
+        <v>115</v>
+      </c>
+      <c r="D11" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="A12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="A13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13" t="s">
+        <v>124</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Documents/Short Product Plan.xlsx
+++ b/Documents/Short Product Plan.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\umesh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B788567-BF7A-47C7-AE45-8A14730FBA54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F2DA449-A1AE-4965-BC08-78BD08EA0A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Product Overview" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="166">
   <si>
     <t>Item</t>
   </si>
@@ -64,39 +64,21 @@
     <t>E2</t>
   </si>
   <si>
-    <t>User Authentication</t>
-  </si>
-  <si>
-    <t>Dashboard</t>
-  </si>
-  <si>
     <t>US1</t>
   </si>
   <si>
     <t>US5</t>
   </si>
   <si>
-    <t>As a user, I want to sign up with email and OTP so that I can access my account securely.</t>
-  </si>
-  <si>
-    <t>As a user, I want to view analytics on a dashboard so that I can see trends quickly.</t>
-  </si>
-  <si>
     <t>Must Have</t>
   </si>
   <si>
     <t>Should Have</t>
   </si>
   <si>
-    <t>To Do</t>
-  </si>
-  <si>
     <t>In Progress</t>
   </si>
   <si>
-    <t>Frontend Dev</t>
-  </si>
-  <si>
     <t>US2</t>
   </si>
   <si>
@@ -145,9 +127,6 @@
     <t>User Story/Requirement</t>
   </si>
   <si>
-    <t>Can be a link to document</t>
-  </si>
-  <si>
     <t>v0.1</t>
   </si>
   <si>
@@ -214,15 +193,9 @@
     <t>Major features</t>
   </si>
   <si>
-    <t>Backend Dev team names</t>
-  </si>
-  <si>
     <t>Test Owner</t>
   </si>
   <si>
-    <t>names</t>
-  </si>
-  <si>
     <t>US6</t>
   </si>
   <si>
@@ -236,24 +209,6 @@
   </si>
   <si>
     <t>Technical Requirements</t>
-  </si>
-  <si>
-    <t>Registration screen details</t>
-  </si>
-  <si>
-    <t>Pop Ups once registered</t>
-  </si>
-  <si>
-    <t>Login screen</t>
-  </si>
-  <si>
-    <t>OTP Generation</t>
-  </si>
-  <si>
-    <t>Sending OTP</t>
-  </si>
-  <si>
-    <t>Login Error Screen</t>
   </si>
   <si>
     <t>Demo Status</t>
@@ -414,12 +369,200 @@
   <si>
     <t>Product Team</t>
   </si>
+  <si>
+    <t>Multi-Source Ingestion</t>
+  </si>
+  <si>
+    <t>US4</t>
+  </si>
+  <si>
+    <t>Integration of mobile camera API with the web dashboard for direct JPG/PNG capture.</t>
+  </si>
+  <si>
+    <t>Complete</t>
+  </si>
+  <si>
+    <t>Dev Team A</t>
+  </si>
+  <si>
+    <t>Verify image upload from mobile browser successfully triggers OCR extraction.</t>
+  </si>
+  <si>
+    <t>Shrusti</t>
+  </si>
+  <si>
+    <t>Lead</t>
+  </si>
+  <si>
+    <t>Send a multi-page PDF via WhatsApp; verify system returns a "Received" confirmation.</t>
+  </si>
+  <si>
+    <t>Forward email with 3 distinct invoice attachments; verify all 3 appear in the dashboard.</t>
+  </si>
+  <si>
+    <t>Drag 20 files into the drop-zone; verify concurrent upload progress bars function correctly.</t>
+  </si>
+  <si>
+    <t>Attempt to upload a 60MB file; verify the error toast "File size exceeds 50MB limit."</t>
+  </si>
+  <si>
+    <t>Backend Dev</t>
+  </si>
+  <si>
+    <t>Dev Team B</t>
+  </si>
+  <si>
+    <t>UI/UX</t>
+  </si>
+  <si>
+    <t>Ready</t>
+  </si>
+  <si>
+    <t>Backlog</t>
+  </si>
+  <si>
+    <t>WhatsApp Business API integration; automated listener for .pdf and .jpg attachments.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">IMAP/SMTP mail server listener for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>invoices@invoiceai.in</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with attachment parsing.</t>
+    </r>
+  </si>
+  <si>
+    <t>Implementation of multi-threaded batch upload UI with a 50MB per-file limit.</t>
+  </si>
+  <si>
+    <t>Client-side validation logic to check file size before initiating server-side upload.</t>
+  </si>
+  <si>
+    <t>As an accountant (Ankit), I want to forward client emails to a dedicated address to centralize all invoices.</t>
+  </si>
+  <si>
+    <t>As a user, I want a "File Too Large" warning so I know if a high-resolution scan exceeds system limits.</t>
+  </si>
+  <si>
+    <t>AI Extraction &amp; Validation</t>
+  </si>
+  <si>
+    <t>US8</t>
+  </si>
+  <si>
+    <t>US9</t>
+  </si>
+  <si>
+    <t>US10</t>
+  </si>
+  <si>
+    <t>As a CA (Ankit Kumar), I want the AI to extract Invoice Date and Number so I can skip manual data entry into Tally.</t>
+  </si>
+  <si>
+    <t>Verify extracted date format is standardized to DD/MM/YYYY from various styles.</t>
+  </si>
+  <si>
+    <t>Upload an invoice with a 12-digit GSTIN; verify system flags "Invalid GSTIN format."</t>
+  </si>
+  <si>
+    <t>Upload same bill twice; verify second upload is marked as "Duplicate Detected" in UI.</t>
+  </si>
+  <si>
+    <t>Simulate a math error in invoice; verify "Calculation Mismatch" warning is triggered.</t>
+  </si>
+  <si>
+    <t>Verify that a bill missing an 'Invoice Number' drops the risk score by 20 points.</t>
+  </si>
+  <si>
+    <t>AI Team</t>
+  </si>
+  <si>
+    <t>Trisha</t>
+  </si>
+  <si>
+    <t>Sushmitha</t>
+  </si>
+  <si>
+    <t>Usha Rani</t>
+  </si>
+  <si>
+    <t>Vanita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uma </t>
+  </si>
+  <si>
+    <t>Tanushree</t>
+  </si>
+  <si>
+    <t>Data Science</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>In Review</t>
+  </si>
+  <si>
+    <t>Must have</t>
+  </si>
+  <si>
+    <t>OCR engine must identify invoice_date and invoice_no fields with 90%+ confidence scores.</t>
+  </si>
+  <si>
+    <t>Regex validation for 15-digit GSTIN format; API integration for live GSTIN status check.</t>
+  </si>
+  <si>
+    <t>Implement a hash-matching algorithm using (Vendor Name + Invoice # + Amount) to identify duplicates.</t>
+  </si>
+  <si>
+    <t>Logic to sum (Taxable Value + CGST + SGST) and compare with the extracted "Grand Total."</t>
+  </si>
+  <si>
+    <t>Data Science model to generate 0-100 score based on field extraction confidence and missing data.</t>
+  </si>
+  <si>
+    <t>As a dessert shop owner (Rizwan), I want a "Risk Score" for every batch to see which bills need a manual check.</t>
+  </si>
+  <si>
+    <t>As a retail owner (Sagar), I want to upload photos of paper bills from my mobile so I don't lose physical receipts.</t>
+  </si>
+  <si>
+    <t>As a busy pharmacist (Ravi), I want to forward supplier PDFs via WhatsApp for instant processing.</t>
+  </si>
+  <si>
+    <t>As a restaurant owner (Sujal), I want to bulk upload 50+ scanned files at once to save time at month-end.</t>
+  </si>
+  <si>
+    <t>As a hardware store owner (Deepa ), I want the system to validate Vendor GSTINs to ensure I can claim Input Tax Credit.</t>
+  </si>
+  <si>
+    <t>As a pharmacy owner (Kiran ), I want the AI to detect duplicate medicine bills so I don't overstate my expenses.</t>
+  </si>
+  <si>
+    <t>As a restaurant owner (Syed Ali), I want the system to flag tax calculation errors to check if vendors charged me correctly.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -440,6 +583,11 @@
       <color rgb="FF0A0A0A"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -801,13 +949,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="31.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -815,36 +963,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="100.8">
       <c r="A3" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="187.2" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="187.2">
       <c r="A4" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="129.6">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -855,21 +1003,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="17.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="73.21875" customWidth="1"/>
-    <col min="5" max="5" width="21.33203125" customWidth="1"/>
+    <col min="4" max="4" width="101.88671875" customWidth="1"/>
+    <col min="5" max="5" width="85.33203125" customWidth="1"/>
     <col min="6" max="6" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.44140625" customWidth="1"/>
     <col min="8" max="8" width="11.33203125" customWidth="1"/>
     <col min="9" max="9" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" customWidth="1"/>
+    <col min="10" max="10" width="73.109375" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -880,10 +1028,10 @@
         <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -898,144 +1046,206 @@
         <v>10</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="G3" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>40</v>
+        <v>113</v>
+      </c>
+      <c r="I3" t="s">
+        <v>114</v>
+      </c>
+      <c r="J3" t="s">
+        <v>115</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2">
+        <v>8</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2">
+        <v>8</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J5" t="s">
+        <v>119</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="2">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="J6" t="s">
+        <v>120</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="2">
+        <v>3</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="J7" t="s">
+        <v>121</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -1043,12 +1253,10 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -1058,12 +1266,10 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="2" t="s">
-        <v>78</v>
-      </c>
+      <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -1073,98 +1279,169 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>14</v>
+      <c r="B11" t="s">
+        <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>154</v>
+      </c>
       <c r="F11" s="2" t="s">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="G11" s="2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>22</v>
+        <v>151</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+      <c r="J11" t="s">
+        <v>138</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>155</v>
+      </c>
       <c r="F12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+      <c r="G12" s="2">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" t="s">
+        <v>122</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G13" s="2">
+        <v>5</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I13" t="s">
+        <v>143</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C14" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="2">
+        <v>8</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C15" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="2">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -1173,11 +1450,10 @@
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -1186,87 +1462,88 @@
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11">
       <c r="A20" s="6" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11">
       <c r="C21" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:11" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="20.399999999999999">
       <c r="C22" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E22" s="4"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11">
       <c r="C23" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11">
       <c r="C24" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E24" s="5"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11">
       <c r="B26" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11">
       <c r="C27" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D27" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="C28" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="D29" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -1275,152 +1552,152 @@
     <col min="5" max="5" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3">
         <v>46128</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B4" s="3">
         <v>46129</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B5" s="3">
         <v>46130</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B6" s="3">
         <v>46131</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B7" s="3">
         <v>46132</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B8" s="3">
         <v>46133</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B9" s="3">
         <v>46134</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1435,7 +1712,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A3:D13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="60.21875" customWidth="1"/>
     <col min="2" max="2" width="64" customWidth="1"/>
@@ -1443,129 +1720,129 @@
     <col min="4" max="4" width="25.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B11" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C11" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="D11" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="2" t="s">
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="B12" t="s">
         <v>103</v>
       </c>
-      <c r="D8" t="s">
+      <c r="C12" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="D12" t="s">
         <v>105</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
         <v>106</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B13" t="s">
         <v>107</v>
       </c>
-      <c r="D9" t="s">
+      <c r="C13" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="D13" t="s">
         <v>109</v>
-      </c>
-      <c r="B10" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D10" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B12" t="s">
-        <v>118</v>
-      </c>
-      <c r="C12" t="s">
-        <v>119</v>
-      </c>
-      <c r="D12" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B13" t="s">
-        <v>122</v>
-      </c>
-      <c r="C13" t="s">
-        <v>123</v>
-      </c>
-      <c r="D13" t="s">
-        <v>124</v>
       </c>
     </row>
   </sheetData>
